--- a/artfynd/A 62062-2024 artfynd.xlsx
+++ b/artfynd/A 62062-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>96813357</v>
       </c>
       <c r="B2" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>323467.9037187845</v>
+        <v>323468</v>
       </c>
       <c r="R2" t="n">
-        <v>6473360.942360749</v>
+        <v>6473361</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -752,19 +747,9 @@
           <t>2021-05-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-05-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,53 +777,73 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105509928</v>
+        <v>94289094</v>
       </c>
       <c r="B3" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219955</v>
+        <v>100141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>BÄVE: LILLESJÖN, Boh</t>
+          <t>Skogstjärn 400 m O Lillesjö industriområde, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>323411.192704929</v>
+        <v>323507</v>
       </c>
       <c r="R3" t="n">
-        <v>6473340.374170491</v>
+        <v>6473487</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,27 +867,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1920-01-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1945-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lokaluppgifter från H. Fries 1945 Göteborgs och Bohusläns fanerogamer och ormbunkar - sammanställt av Alistair Auffret för historiska analyser av förändring i utbredningar</t>
+          <t>2021-05-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,37 +881,33 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Robert Petersen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Mora Aronsson</t>
+          <t>Robert Petersen, Tobias Federsel</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Göteborg och Bohusläns flora 1945</t>
+          <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105509952</v>
+        <v>94289111</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,37 +915,62 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>208242</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>BÄVE: LILLESJÖN, Boh</t>
+          <t>Skogstjärn 400 m O Lillesjö industriområde, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>323411.192704929</v>
+        <v>323507</v>
       </c>
       <c r="R4" t="n">
-        <v>6473340.374170491</v>
+        <v>6473487</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,27 +994,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1920-01-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1945-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Lokaluppgifter från H. Fries 1945 Göteborgs och Bohusläns fanerogamer och ormbunkar - sammanställt av Alistair Auffret för historiska analyser av förändring i utbredningar</t>
+          <t>2021-05-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,37 +1008,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Robert Petersen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Mora Aronsson</t>
+          <t>Robert Petersen, Tobias Federsel</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Göteborg och Bohusläns flora 1945</t>
+          <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105509938</v>
+        <v>94289134</v>
       </c>
       <c r="B5" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,37 +1042,58 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>208249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>BÄVE: LILLESJÖN, Boh</t>
+          <t>Skogstjärn 400 m O Lillesjö industriområde, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>323411.192704929</v>
+        <v>323507</v>
       </c>
       <c r="R5" t="n">
-        <v>6473340.374170491</v>
+        <v>6473487</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,27 +1117,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1920-01-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1945-12-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Lokaluppgifter från H. Fries 1945 Göteborgs och Bohusläns fanerogamer och ormbunkar - sammanställt av Alistair Auffret för historiska analyser av förändring i utbredningar</t>
+          <t>2021-05-13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,21 +1131,582 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Robert Petersen, Tobias Federsel</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>94289160</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lillesjö 200 m O Lillesjö industriområde, Boh</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>323403</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6473368</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Robert Petersen, Tobias Federsel</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>105509938</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>BÄVE: LILLESJÖN, Boh</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>323411</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6473340</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>1920-01-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1945-12-31</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Lokaluppgifter från H. Fries 1945 Göteborgs och Bohusläns fanerogamer och ormbunkar - sammanställt av Alistair Auffret för historiska analyser av förändring i utbredningar</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Mora Aronsson</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Via Mora Aronsson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Göteborg och Bohusläns flora 1945</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>105509928</v>
+      </c>
+      <c r="B8" t="n">
+        <v>107908</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>BÄVE: LILLESJÖN, Boh</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>323411</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6473340</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>1920-01-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>1945-12-31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Lokaluppgifter från H. Fries 1945 Göteborgs och Bohusläns fanerogamer och ormbunkar - sammanställt av Alistair Auffret för historiska analyser av förändring i utbredningar</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Göteborg och Bohusläns flora 1945</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>94289181</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lillesjö 200 m O Lillesjö industriområde, Boh</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>323403</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6473368</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Två mindre bestånd i utkanten av kärret Lillesjö.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Robert Petersen, Tobias Federsel</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>105509952</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>BÄVE: LILLESJÖN, Boh</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>323411</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6473340</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>1920-01-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1945-12-31</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lokaluppgifter från H. Fries 1945 Göteborgs och Bohusläns fanerogamer och ormbunkar - sammanställt av Alistair Auffret för historiska analyser av förändring i utbredningar</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Göteborg och Bohusläns flora 1945</t>
         </is>

--- a/artfynd/A 62062-2024 artfynd.xlsx
+++ b/artfynd/A 62062-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96813357</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94289094</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,6 +1043,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94289111</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1151,6 +1171,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94289134</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1270,6 +1295,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94289160</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1376,6 +1406,11 @@
           <t>Göteborg och Bohusläns flora 1945</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105509938</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1482,6 +1517,11 @@
           <t>Göteborg och Bohusläns flora 1945</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105509928</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1605,6 +1645,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94289181</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1711,8 +1756,24 @@
           <t>Göteborg och Bohusläns flora 1945</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105509952</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>